--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N16_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N16_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.51113243877754</v>
+        <v>5.608059021301351</v>
       </c>
       <c r="D2" t="n">
-        <v>2.500258375744379</v>
+        <v>0.4062919860584616</v>
       </c>
       <c r="E2" t="n">
-        <v>15.67532631633855</v>
+        <v>2.547240526405015</v>
       </c>
       <c r="F2" t="n">
-        <v>19.86880904003477</v>
+        <v>3.228681469005651</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>60.40939031781925</v>
+        <v>9.816525926645628</v>
       </c>
       <c r="D3" t="n">
-        <v>83.79309586242276</v>
+        <v>13.6163780776437</v>
       </c>
       <c r="E3" t="n">
-        <v>15.67532631633855</v>
+        <v>2.547240526405015</v>
       </c>
       <c r="F3" t="n">
-        <v>19.86880904003477</v>
+        <v>3.228681469005651</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.00323030521273</v>
+        <v>2.925524924597068</v>
       </c>
       <c r="D4" t="n">
-        <v>39.86164945174379</v>
+        <v>6.477518035908367</v>
       </c>
       <c r="E4" t="n">
-        <v>15.67532631633855</v>
+        <v>2.547240526405015</v>
       </c>
       <c r="F4" t="n">
-        <v>19.86880904003477</v>
+        <v>3.228681469005651</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.50703549846732</v>
+        <v>3.49489326850094</v>
       </c>
       <c r="D5" t="n">
-        <v>20.77958166653191</v>
+        <v>3.376682020811435</v>
       </c>
       <c r="E5" t="n">
-        <v>15.67532631633855</v>
+        <v>2.547240526405015</v>
       </c>
       <c r="F5" t="n">
-        <v>19.86880904003477</v>
+        <v>3.228681469005651</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>10.90240799089816</v>
+        <v>1.771641298520951</v>
       </c>
       <c r="D6" t="n">
-        <v>37.41162546886885</v>
+        <v>6.079389138691188</v>
       </c>
       <c r="E6" t="n">
-        <v>15.67532631633855</v>
+        <v>2.547240526405015</v>
       </c>
       <c r="F6" t="n">
-        <v>19.86880904003477</v>
+        <v>3.228681469005651</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>18.82451858614185</v>
+        <v>3.05898427024805</v>
       </c>
       <c r="D7" t="n">
-        <v>39.14985146475524</v>
+        <v>6.361850863022728</v>
       </c>
       <c r="E7" t="n">
-        <v>15.67532631633855</v>
+        <v>2.547240526405015</v>
       </c>
       <c r="F7" t="n">
-        <v>19.86880904003477</v>
+        <v>3.228681469005651</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>25.59160071024721</v>
+        <v>4.158635115415172</v>
       </c>
       <c r="D8" t="n">
-        <v>31.06207295953072</v>
+        <v>5.047586855923742</v>
       </c>
       <c r="E8" t="n">
-        <v>15.67532631633855</v>
+        <v>2.547240526405015</v>
       </c>
       <c r="F8" t="n">
-        <v>19.86880904003477</v>
+        <v>3.228681469005651</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>11.31205109606565</v>
+        <v>1.838208303110668</v>
       </c>
       <c r="D9" t="n">
-        <v>15.84921590889731</v>
+        <v>2.575497585195814</v>
       </c>
       <c r="E9" t="n">
-        <v>15.67532631633855</v>
+        <v>2.547240526405015</v>
       </c>
       <c r="F9" t="n">
-        <v>19.86880904003477</v>
+        <v>3.228681469005651</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>23.57134652389844</v>
+        <v>3.830343810133496</v>
       </c>
       <c r="D10" t="n">
-        <v>29.83535386377718</v>
+        <v>4.848245002863791</v>
       </c>
       <c r="E10" t="n">
-        <v>15.67532631633855</v>
+        <v>2.547240526405015</v>
       </c>
       <c r="F10" t="n">
-        <v>19.86880904003477</v>
+        <v>3.228681469005651</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>10.08057374672767</v>
+        <v>1.638093233843246</v>
       </c>
       <c r="D11" t="n">
-        <v>4.295196362014896</v>
+        <v>0.6979694088274206</v>
       </c>
       <c r="E11" t="n">
-        <v>15.67532631633855</v>
+        <v>2.547240526405015</v>
       </c>
       <c r="F11" t="n">
-        <v>19.86880904003477</v>
+        <v>3.228681469005651</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>58.0639859381676</v>
+        <v>9.435397714952234</v>
       </c>
       <c r="D12" t="n">
-        <v>21.0671313371384</v>
+        <v>3.42340884228499</v>
       </c>
       <c r="E12" t="n">
-        <v>15.67532631633855</v>
+        <v>2.547240526405015</v>
       </c>
       <c r="F12" t="n">
-        <v>19.86880904003477</v>
+        <v>3.228681469005651</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>31.16539420317264</v>
+        <v>5.064376558015554</v>
       </c>
       <c r="D13" t="n">
-        <v>33.4620460477272</v>
+        <v>5.43758248275567</v>
       </c>
       <c r="E13" t="n">
-        <v>15.67532631633855</v>
+        <v>2.547240526405015</v>
       </c>
       <c r="F13" t="n">
-        <v>19.86880904003477</v>
+        <v>3.228681469005651</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>39.49500828091003</v>
+        <v>6.41793884564788</v>
       </c>
       <c r="D14" t="n">
-        <v>27.03127234415271</v>
+        <v>4.392581755924815</v>
       </c>
       <c r="E14" t="n">
-        <v>15.67532631633855</v>
+        <v>2.547240526405015</v>
       </c>
       <c r="F14" t="n">
-        <v>19.86880904003477</v>
+        <v>3.228681469005651</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>30.45214651492232</v>
+        <v>4.948473808674877</v>
       </c>
       <c r="D15" t="n">
-        <v>29.08170995961009</v>
+        <v>4.725777868436639</v>
       </c>
       <c r="E15" t="n">
-        <v>15.67532631633855</v>
+        <v>2.547240526405015</v>
       </c>
       <c r="F15" t="n">
-        <v>19.86880904003477</v>
+        <v>3.228681469005651</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>43.89068963350483</v>
+        <v>7.132237065444535</v>
       </c>
       <c r="D16" t="n">
-        <v>44.46616359630465</v>
+        <v>7.225751584399506</v>
       </c>
       <c r="E16" t="n">
-        <v>15.67532631633855</v>
+        <v>2.547240526405015</v>
       </c>
       <c r="F16" t="n">
-        <v>19.86880904003477</v>
+        <v>3.228681469005651</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>42.48043994331718</v>
+        <v>6.903071490789042</v>
       </c>
       <c r="D17" t="n">
-        <v>24.53162511867841</v>
+        <v>3.986389081785241</v>
       </c>
       <c r="E17" t="n">
-        <v>15.67532631633855</v>
+        <v>2.547240526405015</v>
       </c>
       <c r="F17" t="n">
-        <v>19.86880904003477</v>
+        <v>3.228681469005651</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>7.161231056999635</v>
+        <v>1.163700046762441</v>
       </c>
       <c r="D18" t="n">
-        <v>70.69294693724747</v>
+        <v>11.48760387730271</v>
       </c>
       <c r="E18" t="n">
-        <v>15.67532631633855</v>
+        <v>2.547240526405015</v>
       </c>
       <c r="F18" t="n">
-        <v>19.86880904003477</v>
+        <v>3.228681469005651</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
